--- a/currentbuild/StructureDefinition-auditevent-encounter-extension.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-encounter-extension.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T06:11:20+00:00</t>
+    <t>2024-06-06T18:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-encounter-extension.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter-extension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T18:49:12+00:00</t>
+    <t>2024-06-11T05:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,7 +322,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.no/fhir/StructureDefinition/auditevent-encounter)
+    <t xml:space="preserve">Reference(http://hl7.no/fhir/StructureDefinition/no-domain-Trustframework-Encounter)
 </t>
   </si>
   <si>
@@ -648,7 +648,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="65.42578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/currentbuild/StructureDefinition-auditevent-encounter-extension.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter-extension.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:22:30+00:00</t>
+    <t>2024-06-11T05:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
